--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-wood-gasification-with-CCS.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-wood-gasification-with-CCS.xlsx
@@ -2279,8 +2279,12 @@
       <c r="A97" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>39</v>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 6%.</t>
+        </is>
       </c>
     </row>
     <row r="98" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2419,7 +2423,7 @@
         <v>37</v>
       </c>
       <c r="B105" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>32</v>
@@ -2533,8 +2537,12 @@
       <c r="A115" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>40</v>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 7%.</t>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2670,7 +2678,7 @@
         <v>37</v>
       </c>
       <c r="B123" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>32</v>
@@ -2784,8 +2792,12 @@
       <c r="A133" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="8" t="s">
-        <v>41</v>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 16%.</t>
+        </is>
       </c>
     </row>
     <row r="134" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2924,7 +2936,7 @@
         <v>37</v>
       </c>
       <c r="B141" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>32</v>
@@ -3038,8 +3050,12 @@
       <c r="A151" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B151" s="8" t="s">
-        <v>42</v>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 40.2 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 21%.</t>
+        </is>
       </c>
     </row>
     <row r="152" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3178,7 +3194,7 @@
         <v>37</v>
       </c>
       <c r="B159" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>32</v>
@@ -3294,8 +3310,12 @@
       <c r="A169" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="8" t="s">
-        <v>43</v>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 18%.</t>
+        </is>
       </c>
     </row>
     <row r="170" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3434,7 +3454,7 @@
         <v>37</v>
       </c>
       <c r="B177" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>32</v>
@@ -3548,8 +3568,12 @@
       <c r="A187" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="8" t="s">
-        <v>44</v>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 24%.</t>
+        </is>
       </c>
     </row>
     <row r="188" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3685,7 +3709,7 @@
         <v>37</v>
       </c>
       <c r="B195" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>32</v>
@@ -3799,8 +3823,12 @@
       <c r="A205" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B205" s="8" t="s">
-        <v>45</v>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 37%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="206" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3939,7 +3967,7 @@
         <v>37</v>
       </c>
       <c r="B213" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>32</v>
@@ -4053,8 +4081,12 @@
       <c r="A223" t="s">
         <v>9</v>
       </c>
-      <c r="B223" t="s">
-        <v>105</v>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from A.E.M. van den Oever, D. Costa, M. Messagie, Prospective life cycle assessment of alternatively fueled heavy-duty trucks, Applied Energy, 2023, https://doi.org/10.1016/j.apenergy.2023.120834. Energy-based allocation between 3 other co-products (diesel, wax and C5-C10 olefins). Allocation key for this co-product: 11%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
@@ -4182,7 +4214,7 @@
         <v>37</v>
       </c>
       <c r="B231" s="3">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C231" t="s">
         <v>32</v>

--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-wood-gasification-with-CCS.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-wood-gasification-with-CCS.xlsx
@@ -4529,8 +4529,12 @@
       <c r="A258" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B258" s="8" t="s">
-        <v>108</v>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS PAIR-LEVEL THROUGHPUT ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, pages S7-S8 and Table S19, states 2900 kg CO per 30 minutes, 8000 operating hours/year and 30 years, for construction represented by a two-reactor unit. EXPLICIT USER-APPROVED BOUNDARY ASSUMPTION: treat 2900 kg per 30 minutes as total output of the COMPLETE TWO-REACTOR UNIT, not per vessel. Then 1/(2900*2*8000*30) = 7.183908045977011E-10 pair units/kg CO, replacing the inconsistent 1.93E-9. The source duty/parallel-vessel interpretation remains ambiguous: if both vessels each deliver this throughput, the dose would be half this value. This reference accounting assumption is not proof of industrial performance. Keep the corrected two-vessel steel recipe, catalyst/zeolite lifetime quantities, CO output and other material/energy flows unchanged. Historical dose statements are superseded only for this coefficient. No new recovery credit or primary/secondary split.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. Density of syngas: 0.470kg/m3 @1 bar. LHV: 23.9 MJ/kg. The source for CO2 is from the gasification step to produce the H2. Hence, it comes free of burden. The CO2, instead of being stored underground, is embodied in the fuel, hence no correction is needed.</t>
+        </is>
       </c>
     </row>
     <row r="259" spans="1:7" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -4606,7 +4610,7 @@
         <v>46</v>
       </c>
       <c r="B263" s="9">
-        <v>1.9300000000000002E-9</v>
+        <v>7.183908045977011e-10</v>
       </c>
       <c r="C263" s="8" t="s">
         <v>8</v>
